--- a/outputs/metrics/weather_summary.xlsx
+++ b/outputs/metrics/weather_summary.xlsx
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4016</v>
+        <v>3651</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2015-08-22</t>
+          <t>2016-08-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
